--- a/avanceSEGMA.xlsx
+++ b/avanceSEGMA.xlsx
@@ -5,10 +5,10 @@
   <workbookPr showInkAnnotation="0" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Webs\netlify-drop-segma\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avitaconstructora-my.sharepoint.com/personal/aolivares_avita_cl/Documents/OT/netlify-drop-segma/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57D95E4F-579E-455A-9FC1-B5C520CF1F05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="119" documentId="7_{30C0E4BA-C577-AA4F-9580-3F64A608DEE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05265786-1A16-494D-A70E-4A96AB9D02C6}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -680,7 +680,7 @@
         <v>3</v>
       </c>
       <c r="B23" s="1">
-        <v>46256</v>
+        <v>46260</v>
       </c>
       <c r="C23" s="3">
         <v>50</v>
@@ -691,7 +691,7 @@
         <v>4</v>
       </c>
       <c r="B24" s="1">
-        <v>46256</v>
+        <v>46260</v>
       </c>
       <c r="C24" s="3">
         <v>35</v>
@@ -702,10 +702,10 @@
         <v>5</v>
       </c>
       <c r="B25" s="1">
-        <v>46256</v>
+        <v>46260</v>
       </c>
       <c r="C25" s="3">
-        <v>33</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -715,8 +715,8 @@
       <c r="B26" s="1">
         <v>46261</v>
       </c>
-      <c r="C26" s="3">
-        <v>65.36</v>
+      <c r="C26">
+        <v>65.400000000000006</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -726,8 +726,8 @@
       <c r="B27" s="1">
         <v>46261</v>
       </c>
-      <c r="C27" s="3">
-        <v>60.56</v>
+      <c r="C27">
+        <v>60.6</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -737,8 +737,8 @@
       <c r="B28" s="1">
         <v>46261</v>
       </c>
-      <c r="C28" s="3">
-        <v>34.119999999999997</v>
+      <c r="C28">
+        <v>34.1</v>
       </c>
     </row>
   </sheetData>

--- a/avanceSEGMA.xlsx
+++ b/avanceSEGMA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30416"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30425"/>
   <workbookPr showInkAnnotation="0" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avitaconstructora-my.sharepoint.com/personal/aolivares_avita_cl/Documents/OT/netlify-drop-segma/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alvar\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="119" documentId="7_{30C0E4BA-C577-AA4F-9580-3F64A608DEE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05265786-1A16-494D-A70E-4A96AB9D02C6}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1D5DF81D-3ABD-4774-BCE1-0C56C7604FD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -705,7 +705,7 @@
         <v>46260</v>
       </c>
       <c r="C25" s="3">
-        <v>34.1</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -713,10 +713,10 @@
         <v>3</v>
       </c>
       <c r="B26" s="1">
-        <v>46261</v>
-      </c>
-      <c r="C26">
-        <v>65.400000000000006</v>
+        <v>46267</v>
+      </c>
+      <c r="C26" s="3">
+        <v>72.709999999999994</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -724,10 +724,10 @@
         <v>4</v>
       </c>
       <c r="B27" s="1">
-        <v>46261</v>
-      </c>
-      <c r="C27">
-        <v>60.6</v>
+        <v>46267</v>
+      </c>
+      <c r="C27" s="3">
+        <v>38.75</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -735,10 +735,10 @@
         <v>5</v>
       </c>
       <c r="B28" s="1">
-        <v>46261</v>
-      </c>
-      <c r="C28">
-        <v>34.1</v>
+        <v>46267</v>
+      </c>
+      <c r="C28" s="3">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
